--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/Hyperlinks.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/Hyperlinks.xlsx
@@ -497,15 +497,15 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink ref="A1" r:id="rId1"/>
-    <x:hyperlink ref="A2" r:id="rId11" tooltip="Click to go to Yahoo!"/>
+    <x:hyperlink ref="A1" r:id="rId11"/>
+    <x:hyperlink ref="A2" r:id="rId13" tooltip="Click to go to Yahoo!"/>
     <x:hyperlink ref="A3" location="'Hyperlinks'!Test.xlsx" display="Link to a file - same folder"/>
-    <x:hyperlink ref="A4" r:id="rId13"/>
-    <x:hyperlink ref="A5" r:id="rId14"/>
+    <x:hyperlink ref="A4" r:id="rId14"/>
+    <x:hyperlink ref="A5" r:id="rId15"/>
     <x:hyperlink ref="A6" location="'Hyperlinks'!B1" display="Link to an address in this worksheet"/>
     <x:hyperlink ref="A7" location="'Second Sheet'!A1" display="Link to an address in another worksheet"/>
     <x:hyperlink ref="A8" location="'Hyperlinks'!B1:C2" tooltip="SquareBox" display="Link to a range in this worksheet"/>
-    <x:hyperlink ref="A9" r:id="rId15"/>
+    <x:hyperlink ref="A9" r:id="rId16"/>
     <x:hyperlink ref="A11" location="'Hyperlinks'!B1:C2" display="Odd looking link"/>
   </x:hyperlinks>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/Hyperlinks.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/Hyperlinks.xlsx
@@ -57,7 +57,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="4">
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
@@ -78,6 +78,13 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
       <x:color rgb="FFFF0000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/Hyperlinks.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/Hyperlinks.xlsx
@@ -438,7 +438,7 @@
   <x:dimension ref="A1:A13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="39.550625000000004" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="37.750625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:1">

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/Hyperlinks.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/Hyperlinks.xlsx
@@ -117,26 +117,26 @@
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="3">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="3">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/Hyperlinks.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/Hyperlinks.xlsx
@@ -496,12 +496,8 @@
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:1">
-      <x:c r="A12" s="0" t="s"/>
-    </x:row>
-    <x:row r="13" spans="1:1">
-      <x:c r="A13" s="0" t="s"/>
-    </x:row>
+    <x:row r="12" spans="1:1"/>
+    <x:row r="13" spans="1:1"/>
   </x:sheetData>
   <x:hyperlinks>
     <x:hyperlink ref="A1" r:id="rId11"/>
